--- a/data/trans_orig/IP07KS_C04_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C04_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse solo/a en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse solo/a, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3911</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4114</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>29,49%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4684</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1763</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4072</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3699</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>32,82%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>513</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7975</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3945</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11585</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>47,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3020</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>948</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5936</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15988</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20522</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6886</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2362</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6711</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4888</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3495</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8832</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16474</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10626</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27172</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7958</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3554</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14060</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>24898</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35686</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>69957</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>53939</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>85330</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>72769</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>52137</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>108811</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>45,68%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>68,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68285</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52494</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84980</t>
+          <t>62662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>141053</t>
+          <t>121994</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>102955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193516</t>
+          <t>140626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>110162</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>94544</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>127148</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>72729</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>40706</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91145</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>45,65%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>57,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>75557</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98177</t>
+          <t>65472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132507</t>
+          <t>86047</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>187889</t>
+          <t>185719</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144864</t>
+          <t>166993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213221</t>
+          <t>205344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4104</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3605</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3523</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3705</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2257</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2685</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2994</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5319</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1161</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4137</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5388</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13178</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7760</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19452</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>24,86%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>36,7%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6461</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>10805</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>28492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>38015</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>32000</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>43579</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>71,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>60,37%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>29876</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>24530</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>33868</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>77,1%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>63,3%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>87,4%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>38248</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32122</t>
+          <t>25722</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43508</t>
+          <t>35681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68124</t>
+          <t>69735</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60666</t>
+          <t>62085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75294</t>
+          <t>76630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9614</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>18860</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>28554</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>9835</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>5338</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>16713</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>91110</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>73827</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>109547</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>40,56%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>82250</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>58789</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>129707</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>39,08%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>88892</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71467</t>
+          <t>51047</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>75555</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>171142</t>
+          <t>153123</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144736</t>
+          <t>131210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229586</t>
+          <t>172989</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>156391</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>138290</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>173545</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>64,25%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>110014</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>69990</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>130953</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>52,27%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>62,22%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>161662</t>
+          <t>115647</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>142272</t>
+          <t>103072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>182435</t>
+          <t>127424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>271676</t>
+          <t>272038</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>224279</t>
+          <t>250450</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297525</t>
+          <t>296114</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
